--- a/HarmDriveData.xlsx
+++ b/HarmDriveData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
         <v>10000</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
         <v>12500</v>
@@ -553,7 +553,7 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>12500</v>
@@ -583,7 +583,7 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>30000</v>
@@ -613,7 +613,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
         <v>13000</v>
@@ -643,7 +643,7 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
         <v>45000</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
         <v>45000</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="G9" t="n">
         <v>135000</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
         <v>47000</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
         <v>2400</v>
@@ -792,12 +792,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="G12" t="n">
         <v>1500</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
         <v>1500</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="G14" t="n">
         <v>1800</v>
@@ -884,12 +884,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="G15" t="n">
         <v>1500</v>
@@ -919,7 +919,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
         <v>2500</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="G17" t="n">
         <v>2400</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
         <v>2500</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="G19" t="n">
         <v>1800</v>
